--- a/XB6A/3. Đắp đất K95 - XB6A.xlsx
+++ b/XB6A/3. Đắp đất K95 - XB6A.xlsx
@@ -152,7 +152,7 @@
     <t xml:space="preserve">PHỤ LỤC KIỂM TRA CAO ĐỘ, KÍCH THƯỚC HÌNH HỌC</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 08.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 08.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Dự án: Xây dựng HTKT Khu tái định cư phục vụ di dân xã Hải Hà, thị xã Nghi Sơn, tỉnh Thanh Hóa.</t>
@@ -255,49 +255,49 @@
     <t xml:space="preserve">                 </t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 09.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 09.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 10.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 10.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 11.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 11.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 12.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 12.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 5 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 13.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 13.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 6 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 14.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 14.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 7 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 15.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 15.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 8 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 16.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 16.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 9 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
@@ -1616,7 +1616,7 @@
             <v xml:space="preserve">Kiểm tra cao độ đường đen đoạn từ Km0+000,00 -:- Km0+126,46</v>
           </cell>
           <cell r="D3" t="str">
-            <v xml:space="preserve">ngày 14 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 20 tháng 08 năm 2026</v>
           </cell>
           <cell r="G3" t="str">
             <v xml:space="preserve">01.NĐXB6A/CVXD </v>
@@ -1630,7 +1630,7 @@
             <v xml:space="preserve">Đào đất xử lý nền đường đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D4" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G4" t="str">
             <v xml:space="preserve">02.NĐXB6A/CVXD </v>
@@ -1644,7 +1644,7 @@
             <v xml:space="preserve">Rải vải địa kỹ thuật đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D5" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G5" t="str">
             <v xml:space="preserve">03.NĐXB6A/CVXD </v>
@@ -1658,7 +1658,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D6" t="str">
-            <v xml:space="preserve">ngày 16 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
           </cell>
           <cell r="G6" t="str">
             <v xml:space="preserve">04.NĐXB6A/CVXD </v>
@@ -1672,7 +1672,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D7" t="str">
-            <v xml:space="preserve">ngày 17 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
           </cell>
           <cell r="G7" t="str">
             <v xml:space="preserve">05.NĐXB6A/CVXD </v>
@@ -1686,7 +1686,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D8" t="str">
-            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
           </cell>
           <cell r="G8" t="str">
             <v xml:space="preserve">06.NĐXB6A/CVXD </v>
@@ -1700,7 +1700,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D9" t="str">
-            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
           </cell>
           <cell r="G9" t="str">
             <v xml:space="preserve">07.NĐXB6A/CVXD </v>
@@ -1714,7 +1714,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D10" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G10" t="str">
             <v xml:space="preserve">08.NĐXB6A/CVXD </v>
@@ -1728,7 +1728,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D11" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G11" t="str">
             <v xml:space="preserve">09.NĐXB6A/CVXD </v>
@@ -1742,7 +1742,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D12" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G12" t="str">
             <v xml:space="preserve">10.NĐXB6A/CVXD </v>
@@ -1756,7 +1756,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D13" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G13" t="str">
             <v xml:space="preserve">11.NĐXB6A/CVXD </v>
@@ -1770,7 +1770,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 5 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D14" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G14" t="str">
             <v xml:space="preserve">12.NĐXB6A/CVXD </v>
@@ -1784,7 +1784,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 6 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D15" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G15" t="str">
             <v xml:space="preserve">13.NĐXB6A/CVXD </v>
@@ -1798,7 +1798,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 7 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D16" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G16" t="str">
             <v xml:space="preserve">14.NĐXB6A/CVXD </v>
@@ -1812,7 +1812,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 8 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D17" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G17" t="str">
             <v xml:space="preserve">15.NĐXB6A/CVXD </v>
@@ -1826,7 +1826,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 9 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D18" t="str">
-            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
           </cell>
           <cell r="G18" t="str">
             <v xml:space="preserve">16.NĐXB6A/CVXD </v>
@@ -1840,7 +1840,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D19" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G19" t="str">
             <v xml:space="preserve">17.NĐXB6A/CVXD </v>
@@ -1854,7 +1854,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 1, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D20" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G20" t="str">
             <v xml:space="preserve">18.NĐXB6A/CVXD </v>
@@ -1868,7 +1868,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D21" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G21" t="str">
             <v xml:space="preserve">19.NĐXB6A/CVXD </v>
@@ -1882,7 +1882,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 2, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D22" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G22" t="str">
             <v xml:space="preserve">20.NĐXB6A/CVXD </v>
@@ -1896,7 +1896,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D23" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G23" t="str">
             <v xml:space="preserve">21.NĐXB6A/CVXD </v>
@@ -1910,7 +1910,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 3, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D24" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G24" t="str">
             <v xml:space="preserve">22.NĐXB6A/CVXD </v>
@@ -1924,7 +1924,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 4, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D25" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G25" t="str">
             <v xml:space="preserve">23.NĐXB6A/CVXD </v>
@@ -1938,7 +1938,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D26" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G26" t="str">
             <v xml:space="preserve">24.NĐXB6A/CVXD </v>
@@ -1952,7 +1952,7 @@
             <v xml:space="preserve">Vệ sinh, thổi bụi mặt đường </v>
           </cell>
           <cell r="D27" t="str">
-            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 11 tháng 09 năm 2026</v>
           </cell>
           <cell r="G27" t="str">
             <v xml:space="preserve">25.NĐXB6A/CVXD </v>
@@ -1966,7 +1966,7 @@
             <v xml:space="preserve">Tưới lớp thấm bám mặt đường, nhựa MC70, lượng nhựa 1kg/m2</v>
           </cell>
           <cell r="D28" t="str">
-            <v xml:space="preserve">ngày 10 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 13 tháng 09 năm 2026</v>
           </cell>
           <cell r="G28" t="str">
             <v xml:space="preserve">26.NĐXB6A/CVXD </v>
@@ -1980,7 +1980,7 @@
             <v xml:space="preserve">Rải thảm mặt đường bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D29" t="str">
-            <v xml:space="preserve">ngày 12 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
           </cell>
           <cell r="G29" t="str">
             <v xml:space="preserve">27.NĐXB6A/CVXD </v>
@@ -1994,7 +1994,7 @@
             <v xml:space="preserve">Bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D30" t="str">
-            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 21 tháng 09 năm 2026</v>
           </cell>
           <cell r="G30" t="str">
             <v xml:space="preserve">28.NĐXB6A/CVXD </v>
@@ -5264,7 +5264,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 12.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 12.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5557,11 +5557,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-12.2424</v>
+        <v>-12.2394</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0076</v>
+        <v>0.0106</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G6</f>
@@ -5569,11 +5569,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>0.636</v>
+        <v>0.716</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.076</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K6</f>
@@ -5581,11 +5581,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>0.722</v>
+        <v>0.805</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.008</v>
+        <v>0.075</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N6</f>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>12.2549</v>
+        <v>12.2426</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0049</v>
+        <v>-0.0074</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O6</f>
@@ -5605,11 +5605,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>0.715</v>
+        <v>0.729</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.075</v>
+        <v>0.089</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="0" t="n">
@@ -5635,11 +5635,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-12.2401</v>
+        <v>-12.2529</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0099</v>
+        <v>-0.0029</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G15</f>
@@ -5647,11 +5647,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>0.647</v>
+        <v>0.613</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.007</v>
+        <v>-0.027</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K15</f>
@@ -5671,11 +5671,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>12.2593</v>
+        <v>12.2396</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0093</v>
+        <v>-0.0104</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O15</f>
@@ -5683,11 +5683,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>0.613</v>
+        <v>0.648</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.027</v>
+        <v>0.008</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="0" t="n">
@@ -5713,11 +5713,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-12.2594</v>
+        <v>-12.2431</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0094</v>
+        <v>0.0069</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G24</f>
@@ -5725,11 +5725,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>0.628</v>
+        <v>0.646</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.022</v>
+        <v>-0.004</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K24</f>
@@ -5737,11 +5737,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>0.793</v>
+        <v>0.766</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.053</v>
+        <v>0.026</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N24</f>
@@ -5749,11 +5749,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>12.2413</v>
+        <v>12.247</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0087</v>
+        <v>-0.003</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O24</f>
@@ -5761,11 +5761,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>0.734</v>
+        <v>0.721</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.084</v>
+        <v>0.071</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="0" t="n">
@@ -5791,11 +5791,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-12.2393</v>
+        <v>-12.2452</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0107</v>
+        <v>0.0048</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">+Chạy!G33</f>
@@ -5803,11 +5803,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>0.683</v>
+        <v>0.728</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.023</v>
+        <v>0.068</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">+Chạy!K33</f>
@@ -5827,11 +5827,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>12.2579</v>
+        <v>12.2593</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0079</v>
+        <v>0.0093</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">+Chạy!O33</f>
@@ -5839,11 +5839,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>0.687</v>
+        <v>0.75</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.027</v>
+        <v>0.09</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="0" t="n">
@@ -5902,11 +5902,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-7.1111</v>
+        <v>-7.1285</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0089</v>
+        <v>-0.0085</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G51</f>
@@ -5914,11 +5914,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>0.671</v>
+        <v>0.665</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K51</f>
@@ -5926,11 +5926,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>0.765</v>
+        <v>0.814</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.005</v>
+        <v>0.054</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N51</f>
@@ -5938,11 +5938,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>12.2445</v>
+        <v>12.2547</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0055</v>
+        <v>0.0047</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O51</f>
@@ -5950,11 +5950,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>0.679</v>
+        <v>0.753</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.009</v>
+        <v>0.083</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="0" t="n">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-11.7631</v>
+        <v>-11.7621</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0031</v>
+        <v>-0.0021</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G60</f>
@@ -5992,11 +5992,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>0.665</v>
+        <v>0.695</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.015</v>
+        <v>0.015</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K60</f>
@@ -6004,11 +6004,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>0.749</v>
+        <v>0.778</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.011</v>
+        <v>0.018</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N60</f>
@@ -6016,11 +6016,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>12.2474</v>
+        <v>12.2444</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0026</v>
+        <v>-0.0056</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O60</f>
@@ -6028,11 +6028,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>0.659</v>
+        <v>0.751</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.021</v>
+        <v>0.071</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="0" t="n">
@@ -6058,11 +6058,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-11.3772</v>
+        <v>-11.3596</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0072</v>
+        <v>0.0104</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G69</f>
@@ -6070,11 +6070,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.079</v>
+        <v>0.08</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K69</f>
@@ -6082,11 +6082,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>0.784</v>
+        <v>0.845</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.014</v>
+        <v>0.075</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N69</f>
@@ -6094,11 +6094,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>12.2411</v>
+        <v>12.2423</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0089</v>
+        <v>-0.0077</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O69</f>
@@ -6106,11 +6106,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>0.671</v>
+        <v>0.748</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.019</v>
+        <v>0.058</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="0" t="n">
@@ -6136,11 +6136,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-10.9913</v>
+        <v>-10.9983</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0013</v>
+        <v>-0.0083</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">+Chạy!G78</f>
@@ -6148,11 +6148,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>0.693</v>
+        <v>0.756</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.003</v>
+        <v>0.066</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">+Chạy!K78</f>
@@ -6160,11 +6160,11 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>0.814</v>
+        <v>0.828</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
       <c r="M30" s="16" t="n">
         <f aca="false">+Chạy!N78</f>
@@ -6172,11 +6172,11 @@
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>12.2527</v>
+        <v>12.2472</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0027</v>
+        <v>-0.0028</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">+Chạy!O78</f>
@@ -6184,11 +6184,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>0.68</v>
+        <v>0.717</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.01</v>
+        <v>0.027</v>
       </c>
       <c r="S30" s="17"/>
       <c r="W30" s="102"/>
@@ -6392,7 +6392,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 12.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 12.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -11560,7 +11560,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 13.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 13.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -11851,11 +11851,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-11.7941</v>
+        <v>-11.7974</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0059</v>
+        <v>0.0026</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G5</f>
@@ -11863,11 +11863,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>0.936</v>
+        <v>0.983</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.043</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K5</f>
@@ -11875,11 +11875,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>1.012</v>
+        <v>1.006</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.018</v>
+        <v>-0.024</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N5</f>
@@ -11887,11 +11887,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>11.7974</v>
+        <v>11.807</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0026</v>
+        <v>0.007</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O5</f>
@@ -11899,11 +11899,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>0.957</v>
+        <v>1.021</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.017</v>
+        <v>0.081</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="0" t="n">
@@ -11929,11 +11929,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-11.791</v>
+        <v>-11.807</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.009</v>
+        <v>-0.007</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G14</f>
@@ -11941,11 +11941,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>0.986</v>
+        <v>0.932</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.046</v>
+        <v>-0.008</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K14</f>
@@ -11953,11 +11953,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>1.017</v>
+        <v>1.034</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.013</v>
+        <v>0.004</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N14</f>
@@ -11977,11 +11977,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>1.014</v>
+        <v>0.969</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.074</v>
+        <v>0.029</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="0" t="n">
@@ -12007,11 +12007,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-11.8084</v>
+        <v>-11.8083</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0084</v>
+        <v>-0.0083</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G23</f>
@@ -12019,11 +12019,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>0.958</v>
+        <v>1.027</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.008</v>
+        <v>0.077</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K23</f>
@@ -12031,11 +12031,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>1.106</v>
+        <v>1.087</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.066</v>
+        <v>0.047</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N23</f>
@@ -12043,11 +12043,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>11.8031</v>
+        <v>11.8024</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O23</f>
@@ -12055,11 +12055,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>0.96</v>
+        <v>0.938</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="0" t="n">
@@ -12085,11 +12085,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-11.7963</v>
+        <v>-11.8087</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0037</v>
+        <v>-0.0087</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">+Chạy!G32</f>
@@ -12097,11 +12097,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>1.05</v>
+        <v>1.045</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.09</v>
+        <v>0.085</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">+Chạy!K32</f>
@@ -12109,11 +12109,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>1.048</v>
+        <v>1.106</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.008</v>
+        <v>0.066</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">+Chạy!N32</f>
@@ -12121,11 +12121,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>11.7935</v>
+        <v>11.7993</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0065</v>
+        <v>-0.0007</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">+Chạy!O32</f>
@@ -12133,11 +12133,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>1.043</v>
+        <v>0.953</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.083</v>
+        <v>-0.007</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="0" t="n">
@@ -12163,11 +12163,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-4.184</v>
+        <v>-4.1866</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.004</v>
+        <v>-0.0066</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">+Chạy!G41</f>
@@ -12175,11 +12175,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>0.935</v>
+        <v>1.017</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.025</v>
+        <v>0.057</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">+Chạy!K41</f>
@@ -12187,11 +12187,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>1.079</v>
+        <v>1.091</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.029</v>
+        <v>0.041</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">+Chạy!N41</f>
@@ -12199,11 +12199,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>6.8592</v>
+        <v>6.8583</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0092</v>
+        <v>0.0083</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">+Chạy!O41</f>
@@ -12211,11 +12211,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>1.024</v>
+        <v>0.948</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.064</v>
+        <v>-0.012</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="0" t="n">
@@ -12241,11 +12241,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-7.4178</v>
+        <v>-7.4097</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0022</v>
+        <v>0.0103</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G50</f>
@@ -12253,11 +12253,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>0.965</v>
+        <v>1.029</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.005</v>
+        <v>0.059</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K50</f>
@@ -12265,11 +12265,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>1.135</v>
+        <v>1.04</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.075</v>
+        <v>-0.02</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N50</f>
@@ -12277,11 +12277,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>11.8052</v>
+        <v>11.8105</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O50</f>
@@ -12289,11 +12289,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>1.045</v>
+        <v>0.982</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.075</v>
+        <v>0.012</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="0" t="n">
@@ -12319,11 +12319,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-11.805</v>
+        <v>-11.8004</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.005</v>
+        <v>-0.0004</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G59</f>
@@ -12331,11 +12331,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>0.989</v>
+        <v>1.006</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.009</v>
+        <v>0.026</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K59</f>
@@ -12343,11 +12343,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>1.093</v>
+        <v>1.099</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N59</f>
@@ -12355,11 +12355,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>11.7949</v>
+        <v>11.8015</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O59</f>
@@ -12367,11 +12367,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>1.05</v>
+        <v>0.959</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.07</v>
+        <v>-0.021</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="0" t="n">
@@ -12397,11 +12397,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-11.4772</v>
+        <v>-11.4822</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0028</v>
+        <v>-0.0022</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G68</f>
@@ -12409,11 +12409,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>1.022</v>
+        <v>1.05</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.032</v>
+        <v>0.06</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K68</f>
@@ -12421,11 +12421,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>1.134</v>
+        <v>1.121</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.064</v>
+        <v>0.051</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N68</f>
@@ -12433,11 +12433,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>11.8074</v>
+        <v>11.8013</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0074</v>
+        <v>0.0013</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O68</f>
@@ -12445,11 +12445,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>0.973</v>
+        <v>0.984</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.017</v>
+        <v>-0.006</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="0" t="n">
@@ -12475,11 +12475,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-11.1099</v>
+        <v>-11.1185</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0001</v>
+        <v>-0.0085</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">+Chạy!G77</f>
@@ -12487,11 +12487,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>1.068</v>
+        <v>1.004</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.078</v>
+        <v>0.014</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">+Chạy!K77</f>
@@ -12499,11 +12499,11 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>1.072</v>
+        <v>1.078</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="M30" s="16" t="n">
         <f aca="false">+Chạy!N77</f>
@@ -12511,11 +12511,11 @@
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>11.802</v>
+        <v>11.799</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">+Chạy!O77</f>
@@ -12523,11 +12523,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>1.05</v>
+        <v>1.019</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.06</v>
+        <v>0.029</v>
       </c>
       <c r="S30" s="17"/>
       <c r="W30" s="102"/>
@@ -12722,7 +12722,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 13.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 13.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -17895,7 +17895,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 14.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 14.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -18187,11 +18187,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-11.3555</v>
+        <v>-11.3458</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0055</v>
+        <v>0.0042</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G4</f>
@@ -18199,11 +18199,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>1.325</v>
+        <v>1.314</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.085</v>
+        <v>0.074</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K4</f>
@@ -18211,11 +18211,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>1.391</v>
+        <v>1.312</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.061</v>
+        <v>-0.018</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N4</f>
@@ -18223,11 +18223,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>11.3565</v>
+        <v>11.3478</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0065</v>
+        <v>-0.0022</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O4</f>
@@ -18235,11 +18235,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>1.285</v>
+        <v>1.313</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.045</v>
+        <v>0.073</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="0" t="n">
@@ -18265,11 +18265,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-11.3456</v>
+        <v>-11.3387</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0044</v>
+        <v>0.0113</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G13</f>
@@ -18277,11 +18277,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>1.223</v>
+        <v>1.316</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.017</v>
+        <v>0.076</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K13</f>
@@ -18289,11 +18289,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>1.376</v>
+        <v>1.391</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N13</f>
@@ -18301,11 +18301,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>11.3504</v>
+        <v>11.3416</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0004</v>
+        <v>-0.0084</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O13</f>
@@ -18313,11 +18313,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>1.282</v>
+        <v>1.261</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.042</v>
+        <v>0.021</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="0" t="n">
@@ -18343,11 +18343,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-11.3526</v>
+        <v>-11.3514</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0026</v>
+        <v>-0.0014</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G22</f>
@@ -18355,11 +18355,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>1.236</v>
+        <v>1.326</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.014</v>
+        <v>0.076</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K22</f>
@@ -18367,11 +18367,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>1.333</v>
+        <v>1.403</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.007</v>
+        <v>0.063</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N22</f>
@@ -18379,11 +18379,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>11.3479</v>
+        <v>11.3445</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0021</v>
+        <v>-0.0055</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O22</f>
@@ -18391,11 +18391,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>1.308</v>
+        <v>1.299</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="0" t="n">
@@ -18421,11 +18421,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-11.3563</v>
+        <v>-11.3429</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0063</v>
+        <v>0.0071</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">+Chạy!G31</f>
@@ -18433,11 +18433,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>1.284</v>
+        <v>1.31</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.024</v>
+        <v>0.05</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">+Chạy!K31</f>
@@ -18445,11 +18445,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>1.37</v>
+        <v>1.313</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.03</v>
+        <v>-0.027</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">+Chạy!N31</f>
@@ -18457,11 +18457,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>11.3524</v>
+        <v>11.3444</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0024</v>
+        <v>-0.0056</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">+Chạy!O31</f>
@@ -18469,11 +18469,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>1.321</v>
+        <v>1.289</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.061</v>
+        <v>0.029</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="0" t="n">
@@ -18499,11 +18499,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-4.4132</v>
+        <v>-4.4139</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0068</v>
+        <v>0.0061</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">+Chạy!G40</f>
@@ -18511,11 +18511,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>1.326</v>
+        <v>1.235</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.066</v>
+        <v>-0.025</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">+Chạy!K40</f>
@@ -18523,11 +18523,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>1.424</v>
+        <v>1.382</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.074</v>
+        <v>0.032</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">+Chạy!N40</f>
@@ -18535,11 +18535,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>7.1147</v>
+        <v>7.1123</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0053</v>
+        <v>-0.0077</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">+Chạy!O40</f>
@@ -18547,11 +18547,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>1.315</v>
+        <v>1.314</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="0" t="n">
@@ -18577,11 +18577,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-7.7275</v>
+        <v>-7.7207</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0075</v>
+        <v>-0.0007</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G49</f>
@@ -18589,11 +18589,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>1.284</v>
+        <v>1.24</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.014</v>
+        <v>-0.03</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K49</f>
@@ -18601,11 +18601,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>1.449</v>
+        <v>1.339</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.089</v>
+        <v>-0.021</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N49</f>
@@ -18613,11 +18613,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>11.3538</v>
+        <v>11.3407</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0038</v>
+        <v>-0.0093</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O49</f>
@@ -18625,11 +18625,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>1.248</v>
+        <v>1.327</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.022</v>
+        <v>0.057</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="0" t="n">
@@ -18655,11 +18655,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-11.3465</v>
+        <v>-11.3516</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0035</v>
+        <v>-0.0016</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G58</f>
@@ -18667,11 +18667,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>1.257</v>
+        <v>1.337</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.023</v>
+        <v>0.057</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K58</f>
@@ -18679,11 +18679,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>1.339</v>
+        <v>1.373</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.021</v>
+        <v>0.013</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N58</f>
@@ -18691,11 +18691,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>11.3455</v>
+        <v>11.3405</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0045</v>
+        <v>-0.0095</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O58</f>
@@ -18703,11 +18703,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>1.276</v>
+        <v>1.366</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.086</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="0" t="n">
@@ -18733,11 +18733,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-11.3396</v>
+        <v>-11.3476</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0104</v>
+        <v>0.0024</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G67</f>
@@ -18745,11 +18745,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>1.272</v>
+        <v>1.35</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.018</v>
+        <v>0.06</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K67</f>
@@ -18757,11 +18757,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>1.427</v>
+        <v>1.342</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.057</v>
+        <v>-0.028</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N67</f>
@@ -18769,11 +18769,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>11.361</v>
+        <v>11.3552</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.011</v>
+        <v>0.0052</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O67</f>
@@ -18781,11 +18781,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>1.338</v>
+        <v>1.353</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.048</v>
+        <v>0.063</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="0" t="n">
@@ -18811,11 +18811,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-11.2192</v>
+        <v>-11.2342</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0108</v>
+        <v>-0.0042</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">+Chạy!G76</f>
@@ -18823,11 +18823,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>1.277</v>
+        <v>1.316</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.013</v>
+        <v>0.026</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">+Chạy!K76</f>
@@ -18835,11 +18835,11 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>1.345</v>
+        <v>1.411</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.025</v>
+        <v>0.041</v>
       </c>
       <c r="M30" s="16" t="n">
         <f aca="false">+Chạy!N76</f>
@@ -18847,11 +18847,11 @@
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>11.349</v>
+        <v>11.3431</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.001</v>
+        <v>-0.0069</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">+Chạy!O76</f>
@@ -18859,11 +18859,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>1.328</v>
+        <v>1.316</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.038</v>
+        <v>0.026</v>
       </c>
       <c r="S30" s="17"/>
       <c r="W30" s="115"/>
@@ -19058,7 +19058,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 14.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 14.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -24232,7 +24232,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 15.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 15.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -24525,11 +24525,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-10.9004</v>
+        <v>-10.9061</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0004</v>
+        <v>-0.0061</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G3</f>
@@ -24537,11 +24537,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>1.62</v>
+        <v>1.542</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.08</v>
+        <v>0.002</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K3</f>
@@ -24549,11 +24549,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N3</f>
@@ -24561,11 +24561,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>10.8899</v>
+        <v>10.9018</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0101</v>
+        <v>0.0018</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O3</f>
@@ -24573,11 +24573,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>1.572</v>
+        <v>1.536</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.032</v>
+        <v>-0.004</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="0" t="n">
@@ -24607,11 +24607,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-10.8896</v>
+        <v>-10.9062</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0104</v>
+        <v>-0.0062</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G12</f>
@@ -24619,11 +24619,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>1.574</v>
+        <v>1.62</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.034</v>
+        <v>0.08</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K12</f>
@@ -24631,11 +24631,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>1.672</v>
+        <v>1.622</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.042</v>
+        <v>-0.008</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N12</f>
@@ -24643,11 +24643,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>10.8945</v>
+        <v>10.8993</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0055</v>
+        <v>-0.0007</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O12</f>
@@ -24655,11 +24655,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>1.575</v>
+        <v>1.587</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.035</v>
+        <v>0.047</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="0" t="n">
@@ -24689,11 +24689,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-10.9053</v>
+        <v>-10.9021</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0053</v>
+        <v>-0.0021</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G21</f>
@@ -24701,11 +24701,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>1.529</v>
+        <v>1.631</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.021</v>
+        <v>0.081</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K21</f>
@@ -24713,11 +24713,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>1.654</v>
+        <v>1.677</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.014</v>
+        <v>0.037</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N21</f>
@@ -24725,11 +24725,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>10.9046</v>
+        <v>10.8944</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0046</v>
+        <v>-0.0056</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O21</f>
@@ -24737,11 +24737,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>1.526</v>
+        <v>1.521</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.024</v>
+        <v>-0.029</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="0" t="n">
@@ -24771,11 +24771,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-10.8959</v>
+        <v>-10.9057</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0041</v>
+        <v>-0.0057</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">+Chạy!G30</f>
@@ -24783,11 +24783,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>1.641</v>
+        <v>1.636</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.081</v>
+        <v>0.076</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">+Chạy!K30</f>
@@ -24795,11 +24795,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>1.697</v>
+        <v>1.664</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.057</v>
+        <v>0.024</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">+Chạy!N30</f>
@@ -24807,11 +24807,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>10.9106</v>
+        <v>10.9012</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0106</v>
+        <v>0.0012</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">+Chạy!O30</f>
@@ -24819,11 +24819,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>1.624</v>
+        <v>1.589</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.064</v>
+        <v>0.029</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="0" t="n">
@@ -24853,11 +24853,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-4.6766</v>
+        <v>-4.6687</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0066</v>
+        <v>0.0013</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">+Chạy!G39</f>
@@ -24865,11 +24865,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>1.599</v>
+        <v>1.563</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.039</v>
+        <v>0.003</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">+Chạy!K39</f>
@@ -24877,11 +24877,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>1.702</v>
+        <v>1.691</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.052</v>
+        <v>0.041</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">+Chạy!N39</f>
@@ -24889,11 +24889,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>10.8919</v>
+        <v>10.9024</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0081</v>
+        <v>0.0024</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">+Chạy!O39</f>
@@ -24901,11 +24901,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>1.547</v>
+        <v>1.629</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.013</v>
+        <v>0.069</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="0" t="n">
@@ -24935,11 +24935,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-8.0167</v>
+        <v>-8.0188</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0033</v>
+        <v>0.0012</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G48</f>
@@ -24947,11 +24947,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>1.651</v>
+        <v>1.596</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.081</v>
+        <v>0.026</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K48</f>
@@ -24959,11 +24959,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>1.722</v>
+        <v>1.63</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.062</v>
+        <v>-0.03</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N48</f>
@@ -24971,11 +24971,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>10.9069</v>
+        <v>10.9029</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0069</v>
+        <v>0.0029</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O48</f>
@@ -24983,11 +24983,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>1.549</v>
+        <v>1.604</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.021</v>
+        <v>0.034</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="0" t="n">
@@ -25017,11 +25017,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-10.9082</v>
+        <v>-10.9025</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0082</v>
+        <v>-0.0025</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G57</f>
@@ -25029,11 +25029,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>1.649</v>
+        <v>1.634</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.069</v>
+        <v>0.054</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K57</f>
@@ -25041,11 +25041,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N57</f>
@@ -25053,11 +25053,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>10.9071</v>
+        <v>10.8942</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0071</v>
+        <v>-0.0058</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O57</f>
@@ -25065,11 +25065,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>1.553</v>
+        <v>1.579</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.027</v>
+        <v>-0.001</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="0" t="n">
@@ -25099,11 +25099,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-10.895</v>
+        <v>-10.9062</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.005</v>
+        <v>-0.0062</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G66</f>
@@ -25111,11 +25111,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>1.586</v>
+        <v>1.621</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.031</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K66</f>
@@ -25123,11 +25123,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>1.74</v>
+        <v>1.682</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.07</v>
+        <v>0.012</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N66</f>
@@ -25135,11 +25135,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>10.8948</v>
+        <v>10.8915</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0052</v>
+        <v>-0.0085</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O66</f>
@@ -25147,11 +25147,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>1.593</v>
+        <v>1.615</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.003</v>
+        <v>0.025</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="0" t="n">
@@ -25181,11 +25181,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-10.8892</v>
+        <v>-10.8942</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0108</v>
+        <v>0.0058</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">+Chạy!G75</f>
@@ -25193,11 +25193,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>1.678</v>
+        <v>1.579</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.088</v>
+        <v>-0.011</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">+Chạy!K75</f>
@@ -25205,11 +25205,11 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>1.756</v>
+        <v>1.738</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.086</v>
+        <v>0.068</v>
       </c>
       <c r="M30" s="16" t="n">
         <f aca="false">+Chạy!N75</f>
@@ -25217,11 +25217,11 @@
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>10.9024</v>
+        <v>10.9056</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0024</v>
+        <v>0.0056</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">+Chạy!O75</f>
@@ -25229,11 +25229,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>1.635</v>
+        <v>1.633</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="S30" s="17"/>
       <c r="X30" s="119"/>
@@ -25442,7 +25442,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 15.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 15.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -30616,7 +30616,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 16.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 16.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -30909,11 +30909,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-10.443</v>
+        <v>-10.4401</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.007</v>
+        <v>0.0099</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G2</f>
@@ -30921,11 +30921,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>1.893</v>
+        <v>1.863</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.053</v>
+        <v>0.023</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K2</f>
@@ -30933,11 +30933,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>2.01</v>
+        <v>1.934</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.08</v>
+        <v>0.004</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N2</f>
@@ -30945,11 +30945,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>10.4458</v>
+        <v>10.4491</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0042</v>
+        <v>-0.0009</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O2</f>
@@ -30957,11 +30957,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>1.845</v>
+        <v>1.816</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.005</v>
+        <v>-0.024</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="0" t="n">
@@ -30991,11 +30991,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-10.4532</v>
+        <v>-10.4557</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0032</v>
+        <v>-0.0057</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G11</f>
@@ -31003,11 +31003,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>1.886</v>
+        <v>1.841</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.046</v>
+        <v>0.001</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K11</f>
@@ -31015,11 +31015,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>1.926</v>
+        <v>2.014</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.084</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N11</f>
@@ -31027,11 +31027,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>10.456</v>
+        <v>10.4579</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.006</v>
+        <v>0.0079</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O11</f>
@@ -31039,11 +31039,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>1.834</v>
+        <v>1.853</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.006</v>
+        <v>0.013</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="0" t="n">
@@ -31073,11 +31073,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-10.4519</v>
+        <v>-10.4467</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0019</v>
+        <v>0.0033</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G20</f>
@@ -31085,11 +31085,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>1.852</v>
+        <v>1.93</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.002</v>
+        <v>0.08</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K20</f>
@@ -31097,11 +31097,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>1.999</v>
+        <v>1.939</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.059</v>
+        <v>-0.001</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N20</f>
@@ -31109,11 +31109,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>10.4441</v>
+        <v>10.4488</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0059</v>
+        <v>-0.0012</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O20</f>
@@ -31121,11 +31121,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>1.837</v>
+        <v>1.906</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.013</v>
+        <v>0.056</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="0" t="n">
@@ -31155,11 +31155,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-10.44</v>
+        <v>-10.4487</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.01</v>
+        <v>0.0013</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">+Chạy!G29</f>
@@ -31167,11 +31167,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>1.929</v>
+        <v>1.834</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.069</v>
+        <v>-0.026</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">+Chạy!K29</f>
@@ -31179,11 +31179,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>1.937</v>
+        <v>1.975</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.003</v>
+        <v>0.035</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">+Chạy!N29</f>
@@ -31191,11 +31191,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>10.4529</v>
+        <v>10.4609</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0029</v>
+        <v>0.0109</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">+Chạy!O29</f>
@@ -31203,11 +31203,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>1.896</v>
+        <v>1.866</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.036</v>
+        <v>0.006</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="0" t="n">
@@ -31237,11 +31237,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-10.4435</v>
+        <v>-10.4584</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0065</v>
+        <v>-0.0084</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">+Chạy!G38</f>
@@ -31249,11 +31249,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>1.866</v>
+        <v>1.925</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.006</v>
+        <v>0.065</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">+Chạy!K38</f>
@@ -31261,11 +31261,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>1.983</v>
+        <v>1.934</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.033</v>
+        <v>-0.016</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">+Chạy!N38</f>
@@ -31273,11 +31273,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>10.4602</v>
+        <v>10.4511</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0102</v>
+        <v>0.0011</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">+Chạy!O38</f>
@@ -31285,11 +31285,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>1.884</v>
+        <v>1.912</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.024</v>
+        <v>0.052</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="0" t="n">
@@ -31319,11 +31319,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-10.4536</v>
+        <v>-10.445</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0036</v>
+        <v>0.005</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G47</f>
@@ -31331,11 +31331,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>1.852</v>
+        <v>1.922</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.018</v>
+        <v>0.052</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K47</f>
@@ -31343,11 +31343,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.042</v>
+        <v>1.953</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.082</v>
+        <v>-0.007</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N47</f>
@@ -31355,11 +31355,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>10.4438</v>
+        <v>10.4497</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0062</v>
+        <v>-0.0003</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O47</f>
@@ -31367,11 +31367,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>1.957</v>
+        <v>1.938</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.087</v>
+        <v>0.068</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="0" t="n">
@@ -31401,11 +31401,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-10.4457</v>
+        <v>-10.4449</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0043</v>
+        <v>0.0051</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G56</f>
@@ -31413,11 +31413,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>1.852</v>
+        <v>1.858</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.028</v>
+        <v>-0.022</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K56</f>
@@ -31425,11 +31425,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>1.938</v>
+        <v>1.973</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.022</v>
+        <v>0.013</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N56</f>
@@ -31437,11 +31437,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>10.4554</v>
+        <v>10.442</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0054</v>
+        <v>-0.008</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O56</f>
@@ -31449,11 +31449,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>1.92</v>
+        <v>1.961</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.04</v>
+        <v>0.081</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="0" t="n">
@@ -31483,11 +31483,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-10.4513</v>
+        <v>-10.4568</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G65</f>
@@ -31495,11 +31495,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>1.87</v>
+        <v>1.979</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.02</v>
+        <v>0.089</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K65</f>
@@ -31507,11 +31507,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.009</v>
+        <v>1.964</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.039</v>
+        <v>-0.006</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N65</f>
@@ -31519,11 +31519,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>10.4519</v>
+        <v>10.4429</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0019</v>
+        <v>-0.0071</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O65</f>
@@ -31531,11 +31531,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>1.892</v>
+        <v>1.918</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.002</v>
+        <v>0.028</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="0" t="n">
@@ -31565,11 +31565,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-10.4404</v>
+        <v>-10.4475</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0096</v>
+        <v>0.0025</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">+Chạy!G74</f>
@@ -31577,11 +31577,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>1.945</v>
+        <v>1.969</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.055</v>
+        <v>0.079</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">+Chạy!K74</f>
@@ -31589,11 +31589,11 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>2.041</v>
+        <v>2.018</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.071</v>
+        <v>0.048</v>
       </c>
       <c r="M30" s="16" t="n">
         <f aca="false">+Chạy!N74</f>
@@ -31601,11 +31601,11 @@
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>10.4468</v>
+        <v>10.4521</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0032</v>
+        <v>0.0021</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">+Chạy!O74</f>
@@ -31613,11 +31613,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>1.958</v>
+        <v>1.979</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.068</v>
+        <v>0.089</v>
       </c>
       <c r="S30" s="17"/>
       <c r="X30" s="119"/>
@@ -31826,7 +31826,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 16.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 16.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -36997,7 +36997,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 08.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 08.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -37346,11 +37346,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-2.5591</v>
+        <v>-2.5707</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0109</v>
+        <v>-0.0007</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G28</f>
@@ -37358,11 +37358,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>-0.494</v>
+        <v>-0.526</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.016</v>
+        <v>-0.016</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K28</f>
@@ -37370,11 +37370,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>-0.428</v>
+        <v>-0.412</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.032</v>
+        <v>0.048</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N28</f>
@@ -37382,11 +37382,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>2.5743</v>
+        <v>2.5694</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0043</v>
+        <v>-0.0006</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O28</f>
@@ -37394,11 +37394,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>-0.431</v>
+        <v>-0.487</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.079</v>
+        <v>0.023</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="18" t="n">
@@ -37422,11 +37422,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-8.296</v>
+        <v>-8.2957</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.004</v>
+        <v>0.0043</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G37</f>
@@ -37434,11 +37434,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>-0.461</v>
+        <v>-0.454</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.079</v>
+        <v>0.086</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K37</f>
@@ -37446,11 +37446,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>-0.471</v>
+        <v>-0.431</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.011</v>
+        <v>0.029</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N37</f>
@@ -37458,11 +37458,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>8.2814</v>
+        <v>8.2891</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0014</v>
+        <v>0.0091</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O37</f>
@@ -37470,11 +37470,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>-0.459</v>
+        <v>-0.505</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.081</v>
+        <v>0.035</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="18" t="n">
@@ -37529,11 +37529,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-5.9241</v>
+        <v>-5.9262</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0041</v>
+        <v>-0.0062</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">+Chạy!G55</f>
@@ -37541,11 +37541,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>-0.48</v>
+        <v>-0.482</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">+Chạy!K55</f>
@@ -37553,11 +37553,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>-0.464</v>
+        <v>-0.467</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.024</v>
+        <v>-0.027</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">+Chạy!N55</f>
@@ -37565,11 +37565,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>8.7861</v>
+        <v>8.7824</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0061</v>
+        <v>0.0024</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">+Chạy!O55</f>
@@ -37577,11 +37577,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>-0.559</v>
+        <v>-0.549</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.029</v>
+        <v>-0.019</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="18" t="n">
@@ -37605,11 +37605,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-8.8061</v>
+        <v>-8.8168</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0039</v>
+        <v>-0.0068</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G64</f>
@@ -37617,11 +37617,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>-0.455</v>
+        <v>-0.437</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.065</v>
+        <v>0.083</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K64</f>
@@ -37629,11 +37629,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>-0.45</v>
+        <v>-0.408</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.01</v>
+        <v>0.032</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N64</f>
@@ -37641,11 +37641,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>8.479</v>
+        <v>8.4751</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.009</v>
+        <v>0.0051</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O64</f>
@@ -37653,11 +37653,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>-0.453</v>
+        <v>-0.535</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.067</v>
+        <v>-0.015</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="18" t="n">
@@ -37681,11 +37681,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-8.8414</v>
+        <v>-8.8461</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0086</v>
+        <v>0.0039</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G73</f>
@@ -37693,11 +37693,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>-0.46</v>
+        <v>-0.486</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.05</v>
+        <v>0.024</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K73</f>
@@ -37705,11 +37705,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>-0.38</v>
+        <v>-0.448</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.05</v>
+        <v>-0.018</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N73</f>
@@ -37717,11 +37717,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>8.374</v>
+        <v>8.3701</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.004</v>
+        <v>0.0001</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O73</f>
@@ -37729,11 +37729,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>-0.486</v>
+        <v>-0.521</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.024</v>
+        <v>-0.011</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="18" t="n">
@@ -37965,7 +37965,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 08.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 08.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -43296,7 +43296,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 09.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 09.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -43621,11 +43621,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-8.1603</v>
+        <v>-8.1771</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0097</v>
+        <v>-0.0071</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G18</f>
@@ -43633,11 +43633,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>-0.183</v>
+        <v>-0.284</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.077</v>
+        <v>-0.024</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K18</f>
@@ -43645,11 +43645,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>-0.106</v>
+        <v>-0.09</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.064</v>
+        <v>0.08</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N18</f>
@@ -43657,11 +43657,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>8.2702</v>
+        <v>8.2685</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0102</v>
+        <v>0.0085</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O18</f>
@@ -43669,11 +43669,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>-0.202</v>
+        <v>-0.215</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.058</v>
+        <v>0.045</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="0" t="n">
@@ -43697,11 +43697,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-8.3064</v>
+        <v>-8.3012</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0064</v>
+        <v>-0.0012</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G27</f>
@@ -43709,11 +43709,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>-0.206</v>
+        <v>-0.217</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.044</v>
+        <v>0.033</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K27</f>
@@ -43721,11 +43721,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>-0.124</v>
+        <v>-0.162</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.036</v>
+        <v>-0.002</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N27</f>
@@ -43733,11 +43733,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>8.3457</v>
+        <v>8.3503</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0043</v>
+        <v>0.0003</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O27</f>
@@ -43745,11 +43745,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>-0.233</v>
+        <v>-0.164</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.017</v>
+        <v>0.086</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="0" t="n">
@@ -43773,11 +43773,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-8.5944</v>
+        <v>-8.604</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0056</v>
+        <v>-0.004</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G36</f>
@@ -43785,11 +43785,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>-0.178</v>
+        <v>-0.218</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.062</v>
+        <v>0.022</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K36</f>
@@ -43797,11 +43797,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>-0.189</v>
+        <v>-0.139</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.029</v>
+        <v>0.021</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N36</f>
@@ -43809,11 +43809,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>8.5773</v>
+        <v>8.5707</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0027</v>
+        <v>-0.0093</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O36</f>
@@ -43821,11 +43821,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>-0.212</v>
+        <v>-0.19</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.028</v>
+        <v>0.05</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="0" t="n">
@@ -43880,11 +43880,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-6.2127</v>
+        <v>-6.2286</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0073</v>
+        <v>-0.0086</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">+Chạy!G54</f>
@@ -43892,11 +43892,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>-0.257</v>
+        <v>-0.15</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.027</v>
+        <v>0.08</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">+Chạy!K54</f>
@@ -43904,11 +43904,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>-0.066</v>
+        <v>-0.144</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.074</v>
+        <v>-0.004</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">+Chạy!N54</f>
@@ -43916,11 +43916,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>13.6072</v>
+        <v>13.597</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0072</v>
+        <v>-0.003</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">+Chạy!O54</f>
@@ -43928,11 +43928,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>-0.149</v>
+        <v>-0.205</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.081</v>
+        <v>0.025</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="0" t="n">
@@ -43956,11 +43956,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-11.4169</v>
+        <v>-11.4223</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0031</v>
+        <v>-0.0023</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G63</f>
@@ -43968,11 +43968,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>-0.145</v>
+        <v>-0.242</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.075</v>
+        <v>-0.022</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K63</f>
@@ -43980,11 +43980,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>-0.066</v>
+        <v>-0.083</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.074</v>
+        <v>0.057</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N63</f>
@@ -43992,11 +43992,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>8.7746</v>
+        <v>8.7756</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0046</v>
+        <v>0.0056</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O63</f>
@@ -44004,11 +44004,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>-0.221</v>
+        <v>-0.215</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.001</v>
+        <v>0.005</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="0" t="n">
@@ -44032,11 +44032,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-11.0185</v>
+        <v>-11.0311</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0115</v>
+        <v>-0.0011</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G72</f>
@@ -44044,11 +44044,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>-0.163</v>
+        <v>-0.165</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K72</f>
@@ -44056,11 +44056,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>-0.146</v>
+        <v>-0.1</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.016</v>
+        <v>0.03</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N72</f>
@@ -44068,11 +44068,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>8.6655</v>
+        <v>8.6728</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0045</v>
+        <v>0.0028</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O72</f>
@@ -44080,11 +44080,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>-0.159</v>
+        <v>-0.156</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="0" t="n">
@@ -44108,11 +44108,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-10.6297</v>
+        <v>-10.6268</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0003</v>
+        <v>0.0032</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G81</f>
@@ -44120,11 +44120,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>-0.233</v>
+        <v>-0.22</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.023</v>
+        <v>-0.01</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K81</f>
@@ -44132,11 +44132,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>-0.144</v>
+        <v>-0.051</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.014</v>
+        <v>0.079</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N81</f>
@@ -44144,11 +44144,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>3.5988</v>
+        <v>3.5958</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0088</v>
+        <v>0.0058</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O81</f>
@@ -44156,11 +44156,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>-0.194</v>
+        <v>-0.113</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.006</v>
+        <v>0.087</v>
       </c>
       <c r="S29" s="17"/>
     </row>
@@ -44380,7 +44380,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 09.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 09.NĐXB6A/CVXD ngày 29 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -49562,7 +49562,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 10.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 10.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -49856,11 +49856,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-13.1477</v>
+        <v>-13.1451</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0023</v>
+        <v>0.0049</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G8</f>
@@ -49868,11 +49868,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>0.128</v>
+        <v>0.046</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.088</v>
+        <v>0.006</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K8</f>
@@ -49880,11 +49880,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>0.198</v>
+        <v>0.109</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.068</v>
+        <v>-0.021</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N8</f>
@@ -49892,11 +49892,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>13.148</v>
+        <v>13.1493</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.002</v>
+        <v>-0.0007</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O8</f>
@@ -49904,11 +49904,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>0.032</v>
+        <v>0.085</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.008</v>
+        <v>0.045</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="0" t="n">
@@ -49932,11 +49932,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-13.1554</v>
+        <v>-13.1471</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0054</v>
+        <v>0.0029</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G17</f>
@@ -49944,11 +49944,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.018</v>
+        <v>-0.016</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K17</f>
@@ -49956,11 +49956,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>0.168</v>
+        <v>0.182</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.038</v>
+        <v>0.052</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N17</f>
@@ -49968,11 +49968,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>13.1412</v>
+        <v>13.1543</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0088</v>
+        <v>0.0043</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O17</f>
@@ -49980,11 +49980,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.005</v>
+        <v>-0.016</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="0" t="n">
@@ -50008,11 +50008,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-13.1442</v>
+        <v>-13.1489</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0058</v>
+        <v>0.0011</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G26</f>
@@ -50020,11 +50020,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.021</v>
+        <v>-0.02</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K26</f>
@@ -50032,11 +50032,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>0.198</v>
+        <v>0.23</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.058</v>
+        <v>0.09</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N26</f>
@@ -50044,11 +50044,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>13.1583</v>
+        <v>13.1417</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0083</v>
+        <v>-0.0083</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O26</f>
@@ -50056,11 +50056,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>0.048</v>
+        <v>0.099</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.002</v>
+        <v>0.049</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="0" t="n">
@@ -50084,11 +50084,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-13.1516</v>
+        <v>-13.1504</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">+Chạy!G35</f>
@@ -50096,11 +50096,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>0.059</v>
+        <v>0.129</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.001</v>
+        <v>0.069</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">+Chạy!K35</f>
@@ -50108,11 +50108,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>0.149</v>
+        <v>0.222</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.009</v>
+        <v>0.082</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">+Chạy!N35</f>
@@ -50120,11 +50120,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>13.1569</v>
+        <v>13.1511</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0069</v>
+        <v>0.0011</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">+Chạy!O35</f>
@@ -50132,11 +50132,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>0.092</v>
+        <v>0.049</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.032</v>
+        <v>-0.011</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="0" t="n">
@@ -50191,11 +50191,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-6.5158</v>
+        <v>-6.5148</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0042</v>
+        <v>0.0052</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G53</f>
@@ -50203,11 +50203,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>0.095</v>
+        <v>0.113</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.025</v>
+        <v>0.043</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K53</f>
@@ -50215,11 +50215,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>0.156</v>
+        <v>0.163</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N53</f>
@@ -50227,11 +50227,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>13.1462</v>
+        <v>13.1551</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0038</v>
+        <v>0.0051</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O53</f>
@@ -50239,11 +50239,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>0.101</v>
+        <v>0.11</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.031</v>
+        <v>0.04</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="0" t="n">
@@ -50267,11 +50267,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-11.5324</v>
+        <v>-11.5341</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0024</v>
+        <v>-0.0041</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G62</f>
@@ -50279,11 +50279,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>0.104</v>
+        <v>0.133</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.024</v>
+        <v>0.053</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K62</f>
@@ -50291,11 +50291,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>0.141</v>
+        <v>0.211</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.019</v>
+        <v>0.051</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N62</f>
@@ -50303,11 +50303,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>13.1551</v>
+        <v>13.1405</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0051</v>
+        <v>-0.0095</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O62</f>
@@ -50315,11 +50315,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>0.086</v>
+        <v>0.123</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.006</v>
+        <v>0.043</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="0" t="n">
@@ -50343,11 +50343,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-11.1492</v>
+        <v>-11.1439</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0092</v>
+        <v>-0.0039</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G71</f>
@@ -50355,11 +50355,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>0.066</v>
+        <v>0.104</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.024</v>
+        <v>0.014</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K71</f>
@@ -50367,11 +50367,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>0.151</v>
+        <v>0.183</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.019</v>
+        <v>0.013</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N71</f>
@@ -50379,11 +50379,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>13.1422</v>
+        <v>13.154</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0078</v>
+        <v>0.004</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O71</f>
@@ -50391,11 +50391,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>0.104</v>
+        <v>0.171</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.014</v>
+        <v>0.081</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="0" t="n">
@@ -50419,11 +50419,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-10.7495</v>
+        <v>-10.7474</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0005</v>
+        <v>0.0026</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">+Chạy!G80</f>
@@ -50431,11 +50431,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>0.178</v>
+        <v>0.077</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.088</v>
+        <v>-0.013</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">+Chạy!K80</f>
@@ -50443,11 +50443,11 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>0.156</v>
+        <v>0.187</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.014</v>
+        <v>0.017</v>
       </c>
       <c r="M30" s="16" t="n">
         <f aca="false">+Chạy!N80</f>
@@ -50455,11 +50455,11 @@
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>13.1552</v>
+        <v>13.1488</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0052</v>
+        <v>-0.0012</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">+Chạy!O80</f>
@@ -50467,11 +50467,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>0.136</v>
+        <v>0.115</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.046</v>
+        <v>0.025</v>
       </c>
       <c r="S30" s="17"/>
     </row>
@@ -50665,7 +50665,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 10.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 10.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -55837,7 +55837,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 11.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 11.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -56132,11 +56132,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">+D22+F22</f>
-        <v>-12.7059</v>
+        <v>-12.6895</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0059</v>
+        <v>0.0105</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">+Chạy!G7</f>
@@ -56144,11 +56144,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>0.31</v>
+        <v>0.406</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.03</v>
+        <v>0.066</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">+Chạy!K7</f>
@@ -56156,11 +56156,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>0.426</v>
+        <v>0.441</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.011</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">+Chạy!N7</f>
@@ -56168,11 +56168,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">+M22+O22</f>
-        <v>12.7049</v>
+        <v>12.7111</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0049</v>
+        <v>0.0111</v>
       </c>
       <c r="P22" s="16" t="n">
         <f aca="false">+Chạy!O7</f>
@@ -56180,11 +56180,11 @@
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">P22+R22</f>
-        <v>0.419</v>
+        <v>0.413</v>
       </c>
       <c r="R22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.079</v>
+        <v>0.073</v>
       </c>
       <c r="S22" s="17"/>
       <c r="T22" s="1" t="n">
@@ -56210,11 +56210,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-12.6996</v>
+        <v>-12.7039</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0004</v>
+        <v>-0.0039</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">+Chạy!G16</f>
@@ -56222,11 +56222,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>0.42</v>
+        <v>0.324</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.08</v>
+        <v>-0.016</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">+Chạy!K16</f>
@@ -56234,11 +56234,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>0.445</v>
+        <v>0.468</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.015</v>
+        <v>0.038</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">+Chạy!N16</f>
@@ -56246,11 +56246,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>12.6947</v>
+        <v>12.7013</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0053</v>
+        <v>0.0013</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">+Chạy!O16</f>
@@ -56258,11 +56258,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>0.37</v>
+        <v>0.352</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="1" t="n">
@@ -56288,11 +56288,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-12.6905</v>
+        <v>-12.702</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0095</v>
+        <v>-0.002</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">+Chạy!G25</f>
@@ -56300,11 +56300,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>0.35</v>
+        <v>0.386</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">+Chạy!K25</f>
@@ -56312,11 +56312,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">+Chạy!N25</f>
@@ -56324,11 +56324,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>12.6991</v>
+        <v>12.7045</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0009</v>
+        <v>0.0045</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">+Chạy!O25</f>
@@ -56336,11 +56336,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>0.406</v>
+        <v>0.34</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.056</v>
+        <v>-0.01</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="1" t="n">
@@ -56366,11 +56366,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-12.7105</v>
+        <v>-12.6973</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0105</v>
+        <v>0.0027</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">+Chạy!G34</f>
@@ -56378,11 +56378,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>0.379</v>
+        <v>0.361</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.019</v>
+        <v>0.001</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">+Chạy!K34</f>
@@ -56390,11 +56390,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>0.438</v>
+        <v>0.45</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.002</v>
+        <v>0.01</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">+Chạy!N34</f>
@@ -56402,11 +56402,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>12.6998</v>
+        <v>12.7097</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0002</v>
+        <v>0.0097</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">+Chạy!O34</f>
@@ -56414,11 +56414,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>0.416</v>
+        <v>0.383</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.056</v>
+        <v>0.023</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="1" t="n">
@@ -56477,11 +56477,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-6.8098</v>
+        <v>-6.8276</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0102</v>
+        <v>-0.0076</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">+Chạy!G52</f>
@@ -56489,11 +56489,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>0.448</v>
+        <v>0.419</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.078</v>
+        <v>0.049</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">+Chạy!K52</f>
@@ -56501,11 +56501,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>0.54</v>
+        <v>0.483</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.08</v>
+        <v>0.023</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">+Chạy!N52</f>
@@ -56513,11 +56513,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>12.6952</v>
+        <v>12.7088</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0048</v>
+        <v>0.0088</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">+Chạy!O52</f>
@@ -56525,11 +56525,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>0.347</v>
+        <v>0.451</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.023</v>
+        <v>0.081</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="1" t="n">
@@ -56555,11 +56555,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-11.6545</v>
+        <v>-11.6539</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0045</v>
+        <v>-0.0039</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">+Chạy!G61</f>
@@ -56567,11 +56567,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>0.467</v>
+        <v>0.373</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.087</v>
+        <v>-0.007</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">+Chạy!K61</f>
@@ -56579,11 +56579,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>0.497</v>
+        <v>0.435</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.037</v>
+        <v>-0.025</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">+Chạy!N61</f>
@@ -56591,11 +56591,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>12.6981</v>
+        <v>12.7106</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0019</v>
+        <v>0.0106</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">+Chạy!O61</f>
@@ -56603,11 +56603,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>0.386</v>
+        <v>0.432</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.006</v>
+        <v>0.052</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="1" t="n">
@@ -56633,11 +56633,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-11.2491</v>
+        <v>-11.24</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0009</v>
+        <v>0.01</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">+Chạy!G70</f>
@@ -56645,11 +56645,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>0.455</v>
+        <v>0.438</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.065</v>
+        <v>0.048</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">+Chạy!K70</f>
@@ -56657,11 +56657,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>0.514</v>
+        <v>0.475</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.044</v>
+        <v>0.005</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">+Chạy!N70</f>
@@ -56669,11 +56669,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>12.6994</v>
+        <v>12.7103</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0006</v>
+        <v>0.0103</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">+Chạy!O70</f>
@@ -56681,11 +56681,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>0.397</v>
+        <v>0.383</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.007</v>
+        <v>-0.007</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="1" t="n">
@@ -56711,11 +56711,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-10.8775</v>
+        <v>-10.8699</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0075</v>
+        <v>0.0001</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">+Chạy!G79</f>
@@ -56723,11 +56723,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>0.384</v>
+        <v>0.375</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.006</v>
+        <v>-0.015</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">+Chạy!K79</f>
@@ -56735,11 +56735,11 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>0.496</v>
+        <v>0.525</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.026</v>
+        <v>0.055</v>
       </c>
       <c r="M30" s="16" t="n">
         <f aca="false">+Chạy!N79</f>
@@ -56747,11 +56747,11 @@
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>12.69</v>
+        <v>12.7003</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.01</v>
+        <v>0.0003</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">+Chạy!O79</f>
@@ -56759,11 +56759,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>0.399</v>
+        <v>0.421</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.009</v>
+        <v>0.031</v>
       </c>
       <c r="S30" s="17"/>
       <c r="W30" s="102"/>
@@ -56958,7 +56958,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 11.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 11.NĐXB6A/CVXD ngày 30 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
